--- a/output/pdf_financials_xlsx/BETR.xlsx
+++ b/output/pdf_financials_xlsx/BETR.xlsx
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.20829</v>
+        <v>0.247826</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.193495</v>
+        <v>0.205139</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.201621</v>
+        <v>0.204477</v>
       </c>
     </row>
     <row r="49">
@@ -1398,14 +1398,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
-        <v>0.247826</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>0.205139</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0.204477</v>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1657,13 +1663,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.07692</v>
+        <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.019824</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.015426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1677,14 +1683,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n">
-        <v>0.07692</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>0.019824</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0.015426</v>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -2308,13 +2320,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>25.581211</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>27.714189</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>27.902617</v>
       </c>
     </row>
     <row r="93">
@@ -3292,7 +3304,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3786,7 +3798,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BETR.xlsx
+++ b/output/pdf_financials_xlsx/BETR.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6.20717</v>
+        <v>9.460653000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.970757</v>
+        <v>3.240241</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.546792</v>
+        <v>5.000113</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.255654</v>
+        <v>1.607739</v>
       </c>
     </row>
     <row r="11">
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.037384</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00818</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.01257</v>
       </c>
     </row>
     <row r="35">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.037384</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00818</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.01257</v>
       </c>
     </row>
     <row r="37">
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.247826</v>
+        <v>0.170906</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.205139</v>
+        <v>0.185315</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.204477</v>
+        <v>0.189051</v>
       </c>
     </row>
     <row r="49">
@@ -1398,20 +1398,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C49" s="3" t="n">
+        <v>0.247826</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.205139</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.204477</v>
       </c>
     </row>
     <row r="50">
@@ -1663,13 +1657,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0</v>
+        <v>0.07692</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0</v>
+        <v>0.019824</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0</v>
+        <v>0.015426</v>
       </c>
     </row>
     <row r="62">
@@ -1683,20 +1677,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C62" s="3" t="n">
+        <v>0.07692</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.019824</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.015426</v>
       </c>
     </row>
     <row r="63">
@@ -3232,7 +3220,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3304,7 +3292,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5714,7 +5702,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -5942,7 +5930,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">

--- a/output/pdf_financials_xlsx/BETR.xlsx
+++ b/output/pdf_financials_xlsx/BETR.xlsx
@@ -2645,16 +2645,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.055687</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.005353</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.154387</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.077547</v>
       </c>
     </row>
     <row r="111">
@@ -4244,7 +4244,11 @@
           <t>Accretion expense (Notes 5 and 6)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -5144,7 +5148,11 @@
           <t>Accretion expense (Notes 6 and 7)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.055687</v>
       </c>
